--- a/templates/Prospeccion.xlsx
+++ b/templates/Prospeccion.xlsx
@@ -3,17 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Reporte" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Reporte" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Reporte!$A$2:$AA$13</definedName>
   </definedNames>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TG16tOamYghseX2I0y9+GbTn+2aFTXYcp1OTxFhYxic="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -281,6 +276,10 @@
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -499,15 +498,15 @@
     <col customWidth="1" min="13" max="13" width="37.0"/>
     <col customWidth="1" min="14" max="14" width="43.0"/>
     <col customWidth="1" min="15" max="15" width="29.0"/>
-    <col customWidth="1" min="16" max="16" width="20.0"/>
-    <col customWidth="1" min="17" max="18" width="13.0"/>
+    <col customWidth="1" min="16" max="17" width="20.0"/>
+    <col customWidth="1" min="18" max="18" width="20.57"/>
     <col customWidth="1" min="19" max="19" width="30.0"/>
     <col customWidth="1" min="20" max="20" width="35.0"/>
     <col customWidth="1" min="21" max="21" width="42.0"/>
-    <col customWidth="1" min="22" max="22" width="27.0"/>
+    <col customWidth="1" min="22" max="22" width="32.57"/>
     <col customWidth="1" min="23" max="23" width="28.0"/>
     <col customWidth="1" min="24" max="24" width="42.0"/>
-    <col customWidth="1" min="25" max="25" width="27.0"/>
+    <col customWidth="1" min="25" max="25" width="31.43"/>
     <col customWidth="1" min="26" max="26" width="25.0"/>
     <col customWidth="1" min="27" max="27" width="55.0"/>
   </cols>
